--- a/artfynd/A 46919-2023 artfynd.xlsx
+++ b/artfynd/A 46919-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137238070</v>
       </c>
       <c r="B2" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137238074</v>
       </c>
       <c r="B3" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46919-2023 artfynd.xlsx
+++ b/artfynd/A 46919-2023 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -829,11 +825,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 46919-2023 artfynd.xlsx
+++ b/artfynd/A 46919-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137238070</v>
       </c>
       <c r="B2" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137238074</v>
       </c>
       <c r="B3" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46919-2023 artfynd.xlsx
+++ b/artfynd/A 46919-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137238070</v>
       </c>
       <c r="B2" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137238074</v>
       </c>
       <c r="B3" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46919-2023 artfynd.xlsx
+++ b/artfynd/A 46919-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137238070</v>
       </c>
       <c r="B2" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137238074</v>
       </c>
       <c r="B3" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46919-2023 artfynd.xlsx
+++ b/artfynd/A 46919-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137238070</v>
       </c>
       <c r="B2" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137238074</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
